--- a/consent_forms/034_dance_choreography_recording_consent_form--consent_forms.xlsx
+++ b/consent_forms/034_dance_choreography_recording_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mr',_'value':_'mr'}</t>
+          <t>mr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Mr', 'value': 'Mr'}</t>
+          <t>Mr</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mrs',_'value':_'mrs'}</t>
+          <t>mrs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mrs', 'value': 'Mrs'}</t>
+          <t>Mrs</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'ms',_'value':_'ms'}</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Ms', 'value': 'Ms'}</t>
+          <t>Ms</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'dr',_'value':_'dr'}</t>
+          <t>dr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Dr', 'value': 'Dr'}</t>
+          <t>Dr</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'prof',_'value':_'prof'}</t>
+          <t>prof</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Prof', 'value': 'Prof'}</t>
+          <t>Prof</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'dance_class',_'value':_'dance_class'}</t>
+          <t>dance_class</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Dance Class', 'value': 'Dance Class'}</t>
+          <t>Dance Class</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rehearsal',_'value':_'rehearsal'}</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rehearsal', 'value': 'Rehearsal'}</t>
+          <t>Rehearsal</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'parent',_'value':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Parent', 'value': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'guardian',_'value':_'guardian'}</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Guardian', 'value': 'Guardian'}</t>
+          <t>Guardian</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'contact_info',_'value':_'contact_info'}</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Contact Info', 'value': 'Contact Info'}</t>
+          <t>Contact Info</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medical_info',_'value':_'medical_info'}</t>
+          <t>medical_info</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medical Info', 'value': 'Medical Info'}</t>
+          <t>Medical Info</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'submit',_'value':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Submit', 'value': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
